--- a/diseases/d002/1995-1999.xlsx
+++ b/diseases/d002/1995-1999.xlsx
@@ -11543,6 +11543,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11919,6 +11924,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12064,6 +12074,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12209,6 +12224,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12354,6 +12374,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12499,6 +12524,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12644,6 +12674,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12789,6 +12824,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12934,6 +12974,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13079,6 +13124,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13224,6 +13274,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13369,6 +13424,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13904,6 +13964,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14680,6 +14745,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15225,6 +15295,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15770,6 +15845,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16315,6 +16395,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16860,6 +16945,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17405,6 +17495,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17950,6 +18045,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18495,6 +18595,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19040,6 +19145,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19585,6 +19695,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20130,6 +20245,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21065,6 +21185,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21441,6 +21566,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21586,6 +21716,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21731,6 +21866,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21876,6 +22016,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22021,6 +22166,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22166,6 +22316,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22311,6 +22466,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22456,6 +22616,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22601,6 +22766,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22746,6 +22916,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22889,6 +23064,11 @@
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">

--- a/diseases/d002/1995-1999.xlsx
+++ b/diseases/d002/1995-1999.xlsx
@@ -11538,6 +11538,11 @@
       <c r="Q56" t="n">
         <v>0</v>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11550,12 +11555,22 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
@@ -11904,6 +11919,11 @@
       <c r="Q58" t="n">
         <v>0</v>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11916,12 +11936,22 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
@@ -12039,6 +12069,11 @@
       <c r="Q59" t="n">
         <v>0</v>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12051,12 +12086,22 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
@@ -12174,6 +12219,11 @@
       <c r="Q60" t="n">
         <v>0</v>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12186,12 +12236,22 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
@@ -12309,6 +12369,11 @@
       <c r="Q61" t="n">
         <v>0</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12321,12 +12386,22 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR61" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
@@ -12444,6 +12519,11 @@
       <c r="Q62" t="n">
         <v>0</v>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12456,12 +12536,22 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
@@ -12579,6 +12669,11 @@
       <c r="Q63" t="n">
         <v>0</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12591,12 +12686,22 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
@@ -12714,6 +12819,11 @@
       <c r="Q64" t="n">
         <v>0</v>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12726,12 +12836,22 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
@@ -12849,6 +12969,11 @@
       <c r="Q65" t="n">
         <v>0</v>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12861,12 +12986,22 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
@@ -12984,6 +13119,11 @@
       <c r="Q66" t="n">
         <v>0</v>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12996,12 +13136,22 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
@@ -13119,6 +13269,11 @@
       <c r="Q67" t="n">
         <v>0</v>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13131,12 +13286,22 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV67" t="inlineStr">
         <is>
@@ -13254,6 +13419,11 @@
       <c r="Q68" t="n">
         <v>0</v>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13266,12 +13436,22 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
@@ -13779,6 +13959,11 @@
       <c r="Q71" t="n">
         <v>0</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13791,12 +13976,22 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR71" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV71" t="inlineStr">
         <is>
@@ -14545,6 +14740,11 @@
       <c r="Q75" t="n">
         <v>0</v>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14557,12 +14757,22 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
@@ -15080,6 +15290,11 @@
       <c r="Q78" t="n">
         <v>0</v>
       </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15092,12 +15307,22 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
@@ -15615,6 +15840,11 @@
       <c r="Q81" t="n">
         <v>0</v>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15627,12 +15857,22 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
@@ -16150,6 +16390,11 @@
       <c r="Q84" t="n">
         <v>0</v>
       </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16162,12 +16407,22 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
@@ -16685,6 +16940,11 @@
       <c r="Q87" t="n">
         <v>0</v>
       </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16697,12 +16957,22 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
@@ -17220,6 +17490,11 @@
       <c r="Q90" t="n">
         <v>0</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17232,12 +17507,22 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
@@ -17755,6 +18040,11 @@
       <c r="Q93" t="n">
         <v>0</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17767,12 +18057,22 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
@@ -18290,6 +18590,11 @@
       <c r="Q96" t="n">
         <v>0</v>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18302,12 +18607,22 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
@@ -18825,6 +19140,11 @@
       <c r="Q99" t="n">
         <v>0</v>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18837,12 +19157,22 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
@@ -19360,6 +19690,11 @@
       <c r="Q102" t="n">
         <v>0</v>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19372,12 +19707,22 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
@@ -19895,6 +20240,11 @@
       <c r="Q105" t="n">
         <v>0</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19907,12 +20257,22 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
@@ -20820,6 +21180,11 @@
       <c r="Q110" t="n">
         <v>0</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20832,12 +21197,22 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
@@ -21186,6 +21561,11 @@
       <c r="Q112" t="n">
         <v>0</v>
       </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21198,12 +21578,22 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
@@ -21321,6 +21711,11 @@
       <c r="Q113" t="n">
         <v>0</v>
       </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21333,12 +21728,22 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
@@ -21456,6 +21861,11 @@
       <c r="Q114" t="n">
         <v>0</v>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21468,12 +21878,22 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
@@ -21591,6 +22011,11 @@
       <c r="Q115" t="n">
         <v>0</v>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21603,12 +22028,22 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
@@ -21726,6 +22161,11 @@
       <c r="Q116" t="n">
         <v>0</v>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21738,12 +22178,22 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
@@ -21861,6 +22311,11 @@
       <c r="Q117" t="n">
         <v>0</v>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21873,12 +22328,22 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
@@ -21996,6 +22461,11 @@
       <c r="Q118" t="n">
         <v>0</v>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22008,12 +22478,22 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
@@ -22131,6 +22611,11 @@
       <c r="Q119" t="n">
         <v>0</v>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22143,12 +22628,22 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
@@ -22266,6 +22761,11 @@
       <c r="Q120" t="n">
         <v>0</v>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22278,12 +22778,22 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
@@ -22401,6 +22911,11 @@
       <c r="Q121" t="n">
         <v>0</v>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22413,12 +22928,22 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
@@ -22536,6 +23061,11 @@
       <c r="Q122" t="n">
         <v>0</v>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22548,12 +23078,22 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV122" t="inlineStr">
         <is>
